--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН АСПАРУХОВО/РАЙОН АСПАРУХОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,73 +55,58 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>В7243ВР</t>
+  </si>
+  <si>
+    <t>В2525КН</t>
   </si>
   <si>
     <t>В8987ВР</t>
   </si>
   <si>
-    <t>В7243ВР</t>
-  </si>
-  <si>
     <t>В2071ХК</t>
   </si>
   <si>
+    <t>78970155027720519</t>
+  </si>
+  <si>
+    <t>78970155027720493</t>
+  </si>
+  <si>
     <t>78970155027720501</t>
   </si>
   <si>
-    <t>78970155027720519</t>
-  </si>
-  <si>
     <t>78970155027720527</t>
   </si>
   <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>16:18:00</t>
-  </si>
-  <si>
-    <t>16:20:00</t>
-  </si>
-  <si>
-    <t>15:44:00</t>
-  </si>
-  <si>
-    <t>16:15:00</t>
-  </si>
-  <si>
-    <t>09:36:00</t>
-  </si>
-  <si>
-    <t>14:36:00</t>
-  </si>
-  <si>
-    <t>3236615086 3236615086</t>
-  </si>
-  <si>
-    <t>3236621756 3236621756</t>
-  </si>
-  <si>
-    <t>3236730915 3236730915</t>
-  </si>
-  <si>
-    <t>3236731213 3236731213</t>
-  </si>
-  <si>
-    <t>3236955554 3236955554</t>
-  </si>
-  <si>
-    <t>3236987621 3236987621</t>
+    <t>10:12</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>16:51</t>
+  </si>
+  <si>
+    <t>10:16</t>
+  </si>
+  <si>
+    <t>11:52</t>
+  </si>
+  <si>
+    <t>11:15</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН АСПАРУХОВО</t>
@@ -547,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -556,17 +538,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -606,189 +587,174 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46253</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>23.82</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
+        <v>36.85</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.58</v>
       </c>
       <c r="H2" s="1">
-        <v>0.65</v>
+        <v>58.223</v>
       </c>
       <c r="I2" s="1">
-        <v>15.483</v>
+        <v>1.61</v>
       </c>
       <c r="J2" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15.721</v>
-      </c>
-      <c r="L2" t="s">
+        <v>59.329</v>
+      </c>
+      <c r="K2" t="s">
         <v>25</v>
       </c>
+      <c r="L2">
+        <v>84565</v>
+      </c>
       <c r="M2">
-        <v>92092</v>
-      </c>
-      <c r="N2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>254230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46253</v>
+        <v>46269</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
+        <v>43.03</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="H3" s="1">
+        <v>68.41800000000001</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="J3" s="1">
+        <v>69.709</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>335697</v>
+      </c>
+      <c r="M3">
+        <v>255655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="I3" s="1">
-        <v>15.3</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15.6</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3">
-        <v>92092</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46255</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="F4">
+        <v>23.64</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H4" s="1">
+        <v>15.366</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J4" s="1">
+        <v>15.602</v>
+      </c>
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4">
+        <v>92677</v>
+      </c>
+      <c r="M4">
+        <v>255889</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>15.61</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="I4" s="1">
-        <v>10.146</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K4" s="1">
-        <v>10.303</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
-        <v>92245</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46255</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
       </c>
       <c r="F5">
-        <v>39.1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
+        <v>38.16</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.61</v>
       </c>
       <c r="H5" s="1">
-        <v>1.54</v>
+        <v>61.438</v>
       </c>
       <c r="I5" s="1">
-        <v>60.214</v>
+        <v>1.64</v>
       </c>
       <c r="J5" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="K5" s="1">
-        <v>61.387</v>
-      </c>
-      <c r="L5" t="s">
+        <v>62.582</v>
+      </c>
+      <c r="K5" t="s">
         <v>28</v>
       </c>
+      <c r="L5">
+        <v>84942</v>
+      </c>
       <c r="M5">
-        <v>84231</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>258454</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
-        <v>46260</v>
+        <v>46276</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -797,86 +763,80 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
       </c>
       <c r="F6">
-        <v>45.1</v>
-      </c>
-      <c r="G6" t="s">
+        <v>46.24</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="H6" s="1">
+        <v>73.98399999999999</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="J6" s="1">
+        <v>75.371</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6">
+        <v>9306</v>
+      </c>
+      <c r="M6">
+        <v>173107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="I6" s="1">
-        <v>69.905</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="K6" s="1">
-        <v>71.258</v>
-      </c>
-      <c r="L6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6">
-        <v>8755</v>
-      </c>
-      <c r="N6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3">
-        <v>46261</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
       <c r="F7">
-        <v>25.27</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
+        <v>22.76</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.66</v>
       </c>
       <c r="H7" s="1">
-        <v>0.65</v>
+        <v>15.022</v>
       </c>
       <c r="I7" s="1">
-        <v>16.426</v>
+        <v>0.67</v>
       </c>
       <c r="J7" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K7" s="1">
-        <v>16.678</v>
-      </c>
-      <c r="L7" t="s">
+        <v>15.249</v>
+      </c>
+      <c r="K7" t="s">
         <v>30</v>
       </c>
+      <c r="L7">
+        <v>92879</v>
+      </c>
       <c r="M7">
-        <v>92432</v>
-      </c>
-      <c r="N7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>174171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -884,82 +844,82 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:13">
       <c r="A11" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="7">
-        <v>94.2</v>
+        <v>164.28</v>
       </c>
       <c r="C12" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="9">
-        <v>1.54373</v>
+        <v>1.59522</v>
       </c>
       <c r="E12" s="7">
-        <v>145.42</v>
+        <v>262.06</v>
       </c>
       <c r="F12" s="7">
-        <v>148.24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>266.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="7">
-        <v>64.7</v>
+        <v>46.4</v>
       </c>
       <c r="C13" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="9">
-        <v>0.65</v>
+        <v>0.65491</v>
       </c>
       <c r="E13" s="7">
-        <v>42.06</v>
+        <v>30.39</v>
       </c>
       <c r="F13" s="7">
-        <v>42.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>30.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B14" s="11">
-        <v>158.9</v>
+        <v>210.68</v>
       </c>
       <c r="C14" s="12">
         <v>6</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="11">
-        <v>187.48</v>
+        <v>292.45</v>
       </c>
       <c r="F14" s="11">
-        <v>190.94</v>
+        <v>297.84</v>
       </c>
     </row>
   </sheetData>
